--- a/data/south_south_rankings.xlsx
+++ b/data/south_south_rankings.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\E-library\Vowan_Database\Valentine_Site_Clean\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1F66EC6-5CD8-4546-95E2-C55DEAE272BA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{955FE583-86B0-46C1-8FBD-95830BE473CB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" activeTab="2" xr2:uid="{5AED610E-1BCD-4084-BC64-9696F4CB73F8}"/>
   </bookViews>
@@ -4617,7 +4617,7 @@
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="B2" t="s">
         <v>3</v>
@@ -4655,7 +4655,7 @@
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="B3" t="s">
         <v>4</v>
@@ -4693,7 +4693,7 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="B4" t="s">
         <v>5</v>
@@ -4731,7 +4731,7 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="B5" t="s">
         <v>6</v>
@@ -4769,7 +4769,7 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="B6" t="s">
         <v>7</v>
@@ -4807,7 +4807,7 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="B7" t="s">
         <v>8</v>
@@ -4845,7 +4845,7 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>2</v>
+        <v>53</v>
       </c>
       <c r="B8" t="s">
         <v>9</v>
@@ -4883,7 +4883,7 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="B9" t="s">
         <v>12</v>
@@ -4921,7 +4921,7 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="B10" t="s">
         <v>13</v>
@@ -4959,7 +4959,7 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="B11" t="s">
         <v>14</v>
@@ -4997,7 +4997,7 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="B12" t="s">
         <v>15</v>
@@ -5035,7 +5035,7 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="B13" t="s">
         <v>16</v>
@@ -5073,7 +5073,7 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="B14" t="s">
         <v>17</v>
@@ -5111,7 +5111,7 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="B15" t="s">
         <v>18</v>
@@ -5149,7 +5149,7 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="B16" t="s">
         <v>19</v>
@@ -5187,7 +5187,7 @@
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="B17" t="s">
         <v>20</v>
@@ -5225,7 +5225,7 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="B18" t="s">
         <v>21</v>
@@ -5263,7 +5263,7 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="B19" t="s">
         <v>22</v>
@@ -5301,7 +5301,7 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>11</v>
+        <v>56</v>
       </c>
       <c r="B20" t="s">
         <v>23</v>
@@ -5339,7 +5339,7 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="B21" t="s">
         <v>26</v>
@@ -5377,7 +5377,7 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="B22" t="s">
         <v>27</v>
@@ -5415,7 +5415,7 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="B23" t="s">
         <v>28</v>
@@ -5453,7 +5453,7 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="B24" t="s">
         <v>29</v>
@@ -5491,7 +5491,7 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>25</v>
+        <v>61</v>
       </c>
       <c r="B25" t="s">
         <v>30</v>
